--- a/xlsx/vendas.xlsx
+++ b/xlsx/vendas.xlsx
@@ -16,11 +16,14 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>loteId</t>
   </si>
   <si>
+    <t>brinco</t>
+  </si>
+  <si>
     <t>dataVenda</t>
   </si>
   <si>
@@ -39,12 +42,18 @@
     <t>LOTE-2026-01</t>
   </si>
   <si>
+    <t>FK-5006</t>
+  </si>
+  <si>
     <t xml:space="preserve">Talatona Market</t>
   </si>
   <si>
     <t>CARCAÇA</t>
   </si>
   <si>
+    <t>FK-5023</t>
+  </si>
+  <si>
     <t xml:space="preserve">Restaurante Ilha</t>
   </si>
   <si>
@@ -52,6 +61,9 @@
   </si>
   <si>
     <t>LOTE-2026-02</t>
+  </si>
+  <si>
+    <t>FK-3027</t>
   </si>
   <si>
     <t xml:space="preserve">Kero Luanda</t>
@@ -95,8 +107,11 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0"/>
+    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -601,16 +616,17 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="14.00390625"/>
-    <col customWidth="1" min="2" max="2" width="14.57421875"/>
-    <col customWidth="1" min="3" max="3" width="16.28125"/>
+    <col customWidth="1" min="1" max="1" width="15.421875"/>
+    <col customWidth="1" min="2" max="2" width="14.00390625"/>
+    <col customWidth="1" min="3" max="3" width="14.57421875"/>
+    <col customWidth="1" min="4" max="4" width="16.28125"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
@@ -624,65 +640,77 @@
       </c>
       <c r="F1" t="s">
         <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2">
+        <v>7</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="3">
         <v>46108</v>
       </c>
-      <c r="C2" t="s">
-        <v>7</v>
-      </c>
       <c r="D2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="4">
         <v>2000</v>
       </c>
-      <c r="F2" s="3">
+      <c r="G2" s="4">
         <v>3500</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="2">
+        <v>7</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="3">
         <v>46108</v>
       </c>
-      <c r="C3" t="s">
-        <v>9</v>
-      </c>
       <c r="D3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="3">
+        <v>12</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="4">
         <v>500</v>
       </c>
-      <c r="F3" s="3">
+      <c r="G3" s="4">
         <v>4800</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2">
+        <v>14</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="3">
         <v>46108</v>
       </c>
-      <c r="C4" t="s">
-        <v>12</v>
-      </c>
       <c r="D4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E4" s="3">
+        <v>16</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" s="4">
         <v>1200</v>
       </c>
-      <c r="F4" s="3">
+      <c r="G4" s="4">
         <v>3200</v>
       </c>
     </row>
